--- a/artfynd/Kapellöns naturreservat artfynd.xlsx
+++ b/artfynd/Kapellöns naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54136853</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110651103</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204882</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110649493</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019897</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019701</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019898</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204890</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204821</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204893</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204818</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204889</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019696</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2174,6 +2244,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204732</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2281,6 +2356,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204825</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,6 +2472,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79937</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79939</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2615,6 +2705,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204745</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2727,6 +2822,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204754</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2829,6 +2929,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/221060</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2943,6 +3048,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/221061</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3045,6 +3155,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/520220</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3147,6 +3262,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/769346</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3249,6 +3369,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/617039</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3351,6 +3476,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/676689</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3453,6 +3583,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/651476</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3559,6 +3694,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019681</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3661,6 +3801,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/656430</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3777,6 +3922,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/704342</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3879,6 +4029,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/785230</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3981,6 +4136,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/849665</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4097,6 +4257,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/871372</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4199,6 +4364,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/660782</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4315,6 +4485,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/699902</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4421,6 +4596,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019682</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4523,6 +4703,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/848741</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4634,6 +4819,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/719062</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4741,6 +4931,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/867629</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4843,6 +5038,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/720944</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4949,6 +5149,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019678</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5065,6 +5270,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1924177</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5169,6 +5379,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019671</t>
         </is>
       </c>
     </row>
@@ -5283,6 +5498,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89267175</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5394,6 +5614,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2214411</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5501,6 +5726,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204718</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5613,6 +5843,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204810</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5715,6 +5950,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2481231</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5817,6 +6057,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204750</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5919,6 +6164,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204770</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6026,6 +6276,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204746</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6128,6 +6383,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3802569</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6239,6 +6499,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3910275</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6346,6 +6611,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204749</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6448,6 +6718,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3770799</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6559,6 +6834,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3782321</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6666,6 +6946,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204717</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6768,6 +7053,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4218977</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6879,6 +7169,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4233001</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6981,6 +7276,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5219663</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7092,6 +7392,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5266096</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7198,6 +7503,11 @@
           <t>Södertörnsprojektet 1991-1992, inventering av hotade arter</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57019672</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7304,6 +7614,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1646964</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7416,6 +7731,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204778</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7522,6 +7842,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1646965</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7629,6 +7954,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204785</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7736,6 +8066,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204779</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7843,6 +8178,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204786</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7950,8 +8290,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54204784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>